--- a/data/trans_dic/P70B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P70B_R-Clase-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que concilia su vida profesional y laboral</t>
+          <t>Población que concilia su vida profesional y laboral (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,34; 94,58</t>
+          <t>86,81; 94,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,52; 91,79</t>
+          <t>85,57; 91,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,95; 92,49</t>
+          <t>87,84; 92,46</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,7; 91,38</t>
+          <t>82,07; 91,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,27; 92,69</t>
+          <t>85,67; 92,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,57; 90,95</t>
+          <t>85,43; 91,01</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,83; 98,23</t>
+          <t>83,05; 97,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,85; 87,27</t>
+          <t>71,36; 86,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,75; 97,02</t>
+          <t>82,05; 96,8</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,32; 82,68</t>
+          <t>73,98; 82,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,32; 83,19</t>
+          <t>76,27; 83,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,26; 82,22</t>
+          <t>76,53; 82,03</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,73; 89,78</t>
+          <t>78,56; 90,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,64; 93,81</t>
+          <t>82,1; 93,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83,22; 91,82</t>
+          <t>82,96; 91,89</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -822,84 +822,33 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,03; 91,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>83,6; 88,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,6; 89,51</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>86,7%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>85,85%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>86,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>84,18; 91,2</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>83,94; 88,66</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>84,46; 89,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
@@ -914,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -927,7 +876,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que concilia su vida profesional y laboral</t>
+          <t>Población que concilia su vida profesional y laboral (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>306762; 332186</t>
+          <t>304899; 332617</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>270938; 290807</t>
+          <t>271106; 290209</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>587569; 617871</t>
+          <t>586803; 617647</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>250595; 276899</t>
+          <t>248686; 276080</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>217613; 233807</t>
+          <t>216103; 233655</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>475115; 504984</t>
+          <t>474376; 505342</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>403163; 478135</t>
+          <t>404218; 474975</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51360; 63261</t>
+          <t>51725; 63024</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>457164; 542587</t>
+          <t>458829; 541353</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>414767; 461456</t>
+          <t>412899; 462409</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>324424; 353657</t>
+          <t>324220; 354763</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>749795; 808447</t>
+          <t>752457; 806540</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1273,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>186495; 215392</t>
+          <t>188482; 216394</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>308115; 349781</t>
+          <t>306100; 349557</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>509941; 562606</t>
+          <t>508373; 563035</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1351,17 +1300,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3130</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1681222</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1235740</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2916962</t>
         </is>
       </c>
     </row>
@@ -1397,109 +1346,35 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1629338; 1774408</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1203421; 1269492</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2858307; 3024011</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>1414</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>1681222</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1235740</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>2916962</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>1632363; 1768473</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1208383; 1276249</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2853654; 3025574</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P70B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P70B_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,81; 94,7</t>
+          <t>89,11; 95,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,57; 91,6</t>
+          <t>86,4; 92,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,84; 92,46</t>
+          <t>88,93; 93,25</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,07; 91,11</t>
+          <t>82,93; 91,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,67; 92,63</t>
+          <t>86,64; 93,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,43; 91,01</t>
+          <t>86,27; 91,47</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,05; 97,58</t>
+          <t>79,78; 89,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,36; 86,94</t>
+          <t>71,49; 87,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,05; 96,8</t>
+          <t>79,31; 87,64</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,7%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,98; 82,85</t>
+          <t>75,07; 82,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,27; 83,45</t>
+          <t>77,0; 83,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,53; 82,03</t>
+          <t>77,21; 82,35</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>78,56; 90,2</t>
+          <t>80,2; 90,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,1; 93,75</t>
+          <t>81,17; 88,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,96; 91,89</t>
+          <t>82,47; 88,56</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>84,03; 91,51</t>
+          <t>83,46; 87,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83,6; 88,19</t>
+          <t>83,52; 86,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84,6; 89,51</t>
+          <t>83,82; 86,52</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>322816</t>
+          <t>354211</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>282206</t>
+          <t>303060</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>605022</t>
+          <t>657270</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>304899; 332617</t>
+          <t>340484; 363136</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>271106; 290209</t>
+          <t>292259; 311856</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>586803; 617647</t>
+          <t>640599; 671695</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>265226</t>
+          <t>280826</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>226262</t>
+          <t>247002</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491487</t>
+          <t>527828</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>248686; 276080</t>
+          <t>265698; 293276</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>216103; 233655</t>
+          <t>236983; 254365</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>474376; 505342</t>
+          <t>512354; 543248</t>
         </is>
       </c>
     </row>
@@ -1104,17 +1104,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>449091</t>
+          <t>229851</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57944</t>
+          <t>66124</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507035</t>
+          <t>295976</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>404218; 474975</t>
+          <t>214946; 240523</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51725; 63024</t>
+          <t>58793; 71780</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>458829; 541353</t>
+          <t>278914; 308198</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>439513</t>
+          <t>490353</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>339837</t>
+          <t>384027</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>779350</t>
+          <t>874380</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>412899; 462409</t>
+          <t>464883; 511342</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>324220; 354763</t>
+          <t>367866; 399058</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>752457; 806540</t>
+          <t>847004; 903389</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>204577</t>
+          <t>263939</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>329491</t>
+          <t>266004</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>534067</t>
+          <t>529943</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>188482; 216394</t>
+          <t>246125; 276264</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>306100; 349557</t>
+          <t>253287; 276471</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>508373; 563035</t>
+          <t>510419; 548140</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1681222</t>
+          <t>1619180</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1235740</t>
+          <t>1266218</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2916962</t>
+          <t>2885398</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1629338; 1774408</t>
+          <t>1584220; 1651501</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1203421; 1269492</t>
+          <t>1239338; 1286947</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2858307; 3024011</t>
+          <t>2834539; 2926050</t>
         </is>
       </c>
     </row>
